--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488127_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488127_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.8154</v>
+        <v>2.838</v>
       </c>
       <c r="E2" t="n">
-        <v>3.6394</v>
+        <v>4.3911</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.824</v>
+        <v>-1.5531</v>
       </c>
       <c r="G2" t="n">
         <v>0.1157</v>
@@ -610,13 +610,13 @@
         <v>2.9646</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.8949</v>
+        <v>-0.8723</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.1614</v>
+        <v>-0.4097</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.7334000000000001</v>
+        <v>-0.4626</v>
       </c>
       <c r="V2" t="n">
         <v>0.63</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2024</v>
+        <v>0.2494</v>
       </c>
       <c r="E3" t="n">
-        <v>1.2399</v>
+        <v>1.3608</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.0375</v>
+        <v>-1.1114</v>
       </c>
       <c r="G3" t="n">
         <v>0.725</v>
@@ -688,13 +688,13 @@
         <v>2.2234</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0142</v>
+        <v>0.0612</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4203</v>
+        <v>-0.2994</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4345</v>
+        <v>0.3606</v>
       </c>
       <c r="V3" t="n">
         <v>0.9455</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.7352</v>
+        <v>-0.6816</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.7115</v>
+        <v>-0.4609</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0237</v>
+        <v>-0.2207</v>
       </c>
       <c r="G4" t="n">
         <v>0.2201</v>
@@ -766,13 +766,13 @@
         <v>1.1117</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5106000000000001</v>
+        <v>-0.457</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5471</v>
+        <v>-0.2966</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0365</v>
+        <v>-0.1604</v>
       </c>
       <c r="V4" t="n">
         <v>-0.63</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.452</v>
+        <v>-1.6178</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.276</v>
+        <v>-0.4172</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.176</v>
+        <v>-1.2006</v>
       </c>
       <c r="G5" t="n">
         <v>-2.4466</v>
@@ -844,13 +844,13 @@
         <v>1.6676</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2534</v>
+        <v>0.0877</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1269</v>
+        <v>-0.0143</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1266</v>
+        <v>0.102</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.0461</v>
+        <v>-1.7271</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.4928</v>
+        <v>-1.2969</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5533</v>
+        <v>-0.4302</v>
       </c>
       <c r="G6" t="n">
         <v>-2.1157</v>
@@ -922,13 +922,13 @@
         <v>0.1853</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1156</v>
+        <v>0.2033</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1977</v>
+        <v>-0.0019</v>
       </c>
       <c r="U6" t="n">
-        <v>0.08210000000000001</v>
+        <v>0.2052</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.6854</v>
+        <v>-2.5568</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.1075</v>
+        <v>-2.0528</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5779</v>
+        <v>-0.504</v>
       </c>
       <c r="G7" t="n">
         <v>-1.3829</v>
@@ -1000,13 +1000,13 @@
         <v>0.1853</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5613</v>
+        <v>-0.4328</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2189</v>
+        <v>-0.1641</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3425</v>
+        <v>-0.2686</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. CAMPOS CAMPOS</t>
+          <t>J. TORRES VELEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.2992</v>
+        <v>-3.1294</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.9592</v>
+        <v>-1.7881</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.34</v>
+        <v>-1.3413</v>
       </c>
       <c r="G8" t="n">
-        <v>-5.3072</v>
+        <v>-3.0593</v>
       </c>
       <c r="H8" t="n">
-        <v>-4.6802</v>
+        <v>-2.7321</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.627</v>
+        <v>-0.3272</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.5885</v>
+        <v>-1.7191</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.8599</v>
+        <v>-1.2843</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2714</v>
+        <v>-0.4348</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.7187</v>
+        <v>-1.3403</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.8203</v>
+        <v>-1.4478</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.8984</v>
+        <v>0.1076</v>
       </c>
       <c r="P8" t="n">
-        <v>2.0382</v>
+        <v>0.9264</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.9646</v>
+        <v>0.9264</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2848</v>
+        <v>-0.6821</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1293</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4141</v>
+        <v>-0.6131</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.315</v>
+        <v>-0.3144</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.315</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. TORRES VELEZ</t>
+          <t>J. CAMPOS CAMPOS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.3001</v>
+        <v>-3.5088</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.8111</v>
+        <v>-3.0457</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.4891</v>
+        <v>-0.4631</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.0593</v>
+        <v>-5.3072</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.7321</v>
+        <v>-4.6802</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3272</v>
+        <v>-0.627</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.7191</v>
+        <v>-1.5885</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.2843</v>
+        <v>-1.8599</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.4348</v>
+        <v>0.2714</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.3403</v>
+        <v>-3.7187</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.4478</v>
+        <v>-2.8203</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1076</v>
+        <v>-0.8984</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9264</v>
+        <v>2.0382</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9264</v>
+        <v>2.9646</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8528</v>
+        <v>0.0752</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.092</v>
+        <v>-0.2157</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7608</v>
+        <v>0.291</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.3144</v>
+        <v>-0.315</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-0.315</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.3144</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.6492</v>
+        <v>-3.8938</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.4789</v>
+        <v>-1.7727</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.1703</v>
+        <v>-2.1211</v>
       </c>
       <c r="G10" t="n">
         <v>-0.6913</v>
@@ -1234,13 +1234,13 @@
         <v>0.1853</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5974</v>
+        <v>0.3529</v>
       </c>
       <c r="T10" t="n">
-        <v>0.291</v>
+        <v>-0.0028</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3064</v>
+        <v>0.3556</v>
       </c>
       <c r="V10" t="n">
         <v>-1.8877</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P. QUESADA PONS</t>
+          <t>A. TEJADA CAMACHO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.9904</v>
+        <v>-4.3714</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.934</v>
+        <v>-1.668</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.0565</v>
+        <v>-2.7033</v>
       </c>
       <c r="G11" t="n">
-        <v>-5.5551</v>
+        <v>-4.9503</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.9377</v>
+        <v>-2.3943</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.6174</v>
+        <v>-2.556</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.2277</v>
+        <v>0.2823</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.2751</v>
+        <v>0.0429</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.9526</v>
+        <v>0.2394</v>
       </c>
       <c r="M11" t="n">
-        <v>-4.3274</v>
+        <v>-5.2327</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.6626</v>
+        <v>-2.4373</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.6648</v>
+        <v>-2.7954</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.8529</v>
+        <v>-2.7793</v>
       </c>
       <c r="R11" t="n">
         <v>1.8529</v>
       </c>
       <c r="S11" t="n">
-        <v>1.5646</v>
+        <v>0.2465</v>
       </c>
       <c r="T11" t="n">
-        <v>1.1466</v>
+        <v>-0.4299</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4181</v>
+        <v>0.6765</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. TEJADA CAMACHO</t>
+          <t>A. RODRIGUEZ LOPEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.5475</v>
+        <v>-4.493</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.0165</v>
+        <v>-2.0329</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.531</v>
+        <v>-2.4601</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.9503</v>
+        <v>-2.2095</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.3943</v>
+        <v>-1.5459</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.556</v>
+        <v>-0.6635</v>
       </c>
       <c r="J12" t="n">
-        <v>0.2823</v>
+        <v>-0.7534</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0429</v>
+        <v>-0.2664</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2394</v>
+        <v>-0.487</v>
       </c>
       <c r="M12" t="n">
-        <v>-5.2327</v>
+        <v>-1.4561</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.4373</v>
+        <v>-1.2796</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.7954</v>
+        <v>-0.1766</v>
       </c>
       <c r="P12" t="n">
+        <v>0.5558999999999999</v>
+      </c>
+      <c r="Q12" t="n">
         <v>-0.9264</v>
       </c>
-      <c r="Q12" t="n">
-        <v>-2.7793</v>
-      </c>
       <c r="R12" t="n">
-        <v>1.8529</v>
+        <v>1.4823</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0704</v>
+        <v>-0.6367</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7784</v>
+        <v>-0.3531</v>
       </c>
       <c r="U12" t="n">
-        <v>0.8488</v>
+        <v>-0.2835</v>
       </c>
       <c r="V12" t="n">
-        <v>1.2589</v>
+        <v>-2.2027</v>
       </c>
       <c r="W12" t="n">
-        <v>1.2589</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-2.2027</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ LOPEZ</t>
+          <t>P. QUESADA PONS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.0188</v>
+        <v>-4.7197</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.5341</v>
+        <v>-2.5648</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.4847</v>
+        <v>-2.1549</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.2095</v>
+        <v>-5.5551</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.5459</v>
+        <v>-1.9377</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.6635</v>
+        <v>-3.6174</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.7534</v>
+        <v>-1.2277</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.2664</v>
+        <v>-0.2751</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.487</v>
+        <v>-0.9526</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.4561</v>
+        <v>-4.3274</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.2796</v>
+        <v>-1.6626</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.1766</v>
+        <v>-2.6648</v>
       </c>
       <c r="P13" t="n">
-        <v>0.5558999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.9264</v>
+        <v>-1.8529</v>
       </c>
       <c r="R13" t="n">
-        <v>1.4823</v>
+        <v>1.8529</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.1625</v>
+        <v>0.8354</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8542999999999999</v>
+        <v>0.5158</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3082</v>
+        <v>0.3196</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.2027</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.2027</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-28.7061</v>
+        <v>-27.612</v>
       </c>
       <c r="E14" t="n">
-        <v>-12.4423</v>
+        <v>-11.3481</v>
       </c>
       <c r="F14" t="n">
-        <v>-16.264</v>
+        <v>-16.2638</v>
       </c>
       <c r="G14" t="n">
         <v>-26.6571</v>
@@ -1546,13 +1546,13 @@
         <v>17.6023</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.312900000000001</v>
+        <v>-1.2187</v>
       </c>
       <c r="T14" t="n">
-        <v>-2.8349</v>
+        <v>-1.7407</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5222</v>
+        <v>0.5223</v>
       </c>
       <c r="V14" t="n">
         <v>-2.515400000000001</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>9.9846</v>
+        <v>11.1385</v>
       </c>
       <c r="E15" t="n">
-        <v>7.2808</v>
+        <v>7.4766</v>
       </c>
       <c r="F15" t="n">
-        <v>2.7039</v>
+        <v>3.6619</v>
       </c>
       <c r="G15" t="n">
         <v>8.792999999999999</v>
@@ -1624,13 +1624,13 @@
         <v>2.7793</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3636</v>
+        <v>0.7903</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2014</v>
+        <v>-0.0056</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1622</v>
+        <v>0.7958</v>
       </c>
       <c r="V15" t="n">
         <v>0.6289</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6.4813</v>
+        <v>6.0805</v>
       </c>
       <c r="E16" t="n">
-        <v>3.8841</v>
+        <v>3.3944</v>
       </c>
       <c r="F16" t="n">
-        <v>2.5973</v>
+        <v>2.6861</v>
       </c>
       <c r="G16" t="n">
         <v>3.4018</v>
@@ -1702,13 +1702,13 @@
         <v>1.1117</v>
       </c>
       <c r="S16" t="n">
-        <v>1.6534</v>
+        <v>1.2525</v>
       </c>
       <c r="T16" t="n">
-        <v>0.9439</v>
+        <v>0.4542</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7095</v>
+        <v>0.7983</v>
       </c>
       <c r="V16" t="n">
         <v>0.3144</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. CASTILLO ORTEGA</t>
+          <t>A. VALDERRAMA VIDAL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.2424</v>
+        <v>4.3026</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7089</v>
+        <v>3.396</v>
       </c>
       <c r="F17" t="n">
-        <v>3.5336</v>
+        <v>0.9066</v>
       </c>
       <c r="G17" t="n">
-        <v>4.3196</v>
+        <v>4.4521</v>
       </c>
       <c r="H17" t="n">
-        <v>4.5327</v>
+        <v>5.5825</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.2131</v>
+        <v>-1.1304</v>
       </c>
       <c r="J17" t="n">
-        <v>4.9556</v>
+        <v>6.3322</v>
       </c>
       <c r="K17" t="n">
-        <v>4.0017</v>
+        <v>4.921</v>
       </c>
       <c r="L17" t="n">
-        <v>0.9538</v>
+        <v>1.4113</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.636</v>
+        <v>-1.8801</v>
       </c>
       <c r="N17" t="n">
-        <v>0.531</v>
+        <v>0.6616</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.167</v>
+        <v>-2.5417</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.0382</v>
+        <v>-0.7411</v>
       </c>
       <c r="Q17" t="n">
-        <v>-4.6322</v>
+        <v>-2.7793</v>
       </c>
       <c r="R17" t="n">
-        <v>2.594</v>
+        <v>2.0382</v>
       </c>
       <c r="S17" t="n">
-        <v>1.6477</v>
+        <v>0.9072</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0721</v>
+        <v>0.1586</v>
       </c>
       <c r="U17" t="n">
-        <v>1.5755</v>
+        <v>0.7486</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3133</v>
+        <v>-0.3155</v>
       </c>
       <c r="W17" t="n">
-        <v>0.3133</v>
+        <v>-0.3155</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. VALDERRAMA VIDAL</t>
+          <t>A. CASTILLO ORTEGA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.715</v>
+        <v>4.0186</v>
       </c>
       <c r="E18" t="n">
-        <v>3.2001</v>
+        <v>0.7089</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5149</v>
+        <v>3.3098</v>
       </c>
       <c r="G18" t="n">
-        <v>4.4521</v>
+        <v>4.3196</v>
       </c>
       <c r="H18" t="n">
-        <v>5.5825</v>
+        <v>4.5327</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.1304</v>
+        <v>-0.2131</v>
       </c>
       <c r="J18" t="n">
-        <v>6.3322</v>
+        <v>4.9556</v>
       </c>
       <c r="K18" t="n">
-        <v>4.921</v>
+        <v>4.0017</v>
       </c>
       <c r="L18" t="n">
-        <v>1.4113</v>
+        <v>0.9538</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.8801</v>
+        <v>-0.636</v>
       </c>
       <c r="N18" t="n">
-        <v>0.6616</v>
+        <v>0.531</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.5417</v>
+        <v>-1.167</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.7411</v>
+        <v>-2.0382</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.7793</v>
+        <v>-4.6322</v>
       </c>
       <c r="R18" t="n">
-        <v>2.0382</v>
+        <v>2.594</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3196</v>
+        <v>1.4238</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0373</v>
+        <v>0.0721</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3569</v>
+        <v>1.3517</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.3155</v>
+        <v>0.3133</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.3155</v>
+        <v>0.3133</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.5924</v>
+        <v>2.4928</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7741</v>
+        <v>0.97</v>
       </c>
       <c r="F19" t="n">
-        <v>1.8182</v>
+        <v>1.5228</v>
       </c>
       <c r="G19" t="n">
         <v>1.1962</v>
@@ -1936,13 +1936,13 @@
         <v>1.297</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3962</v>
+        <v>0.2966</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4377</v>
+        <v>-0.2419</v>
       </c>
       <c r="U19" t="n">
-        <v>0.8339</v>
+        <v>0.5384</v>
       </c>
       <c r="V19" t="n">
         <v>0.6294</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. GUERRA ZAYAS</t>
+          <t>R. VARELA SANCHEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.1548</v>
+        <v>2.1534</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3654</v>
+        <v>-0.0081</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7894</v>
+        <v>2.1615</v>
       </c>
       <c r="G20" t="n">
-        <v>2.792</v>
+        <v>1.1523</v>
       </c>
       <c r="H20" t="n">
-        <v>1.3097</v>
+        <v>1.5437</v>
       </c>
       <c r="I20" t="n">
-        <v>1.4823</v>
+        <v>-0.3913</v>
       </c>
       <c r="J20" t="n">
-        <v>3.5277</v>
+        <v>1.1736</v>
       </c>
       <c r="K20" t="n">
-        <v>1.5157</v>
+        <v>0.9661999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>2.012</v>
+        <v>0.2074</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.7357</v>
+        <v>-0.0212</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.206</v>
+        <v>0.5774</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.5296999999999999</v>
+        <v>-0.5987</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.4823</v>
+        <v>0.7411</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.7793</v>
+        <v>-0.9264</v>
       </c>
       <c r="R20" t="n">
-        <v>1.297</v>
+        <v>1.6676</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.155</v>
+        <v>-0.055</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.383</v>
+        <v>-0.2552</v>
       </c>
       <c r="U20" t="n">
-        <v>0.228</v>
+        <v>0.2002</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.315</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>0.315</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R. VARELA SANCHEZ</t>
+          <t>R. GUERRA ZAYAS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.0826</v>
+        <v>1.2115</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.4977</v>
+        <v>0.3654</v>
       </c>
       <c r="F21" t="n">
-        <v>1.5803</v>
+        <v>0.8461</v>
       </c>
       <c r="G21" t="n">
-        <v>1.1523</v>
+        <v>2.792</v>
       </c>
       <c r="H21" t="n">
-        <v>1.5437</v>
+        <v>1.3097</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3913</v>
+        <v>1.4823</v>
       </c>
       <c r="J21" t="n">
-        <v>1.1736</v>
+        <v>3.5277</v>
       </c>
       <c r="K21" t="n">
-        <v>0.9661999999999999</v>
+        <v>1.5157</v>
       </c>
       <c r="L21" t="n">
-        <v>0.2074</v>
+        <v>2.012</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.0212</v>
+        <v>-0.7357</v>
       </c>
       <c r="N21" t="n">
-        <v>0.5774</v>
+        <v>-0.206</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5987</v>
+        <v>-0.5296999999999999</v>
       </c>
       <c r="P21" t="n">
-        <v>0.7411</v>
+        <v>-1.4823</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9264</v>
+        <v>-2.7793</v>
       </c>
       <c r="R21" t="n">
-        <v>1.6676</v>
+        <v>1.297</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1259</v>
+        <v>-0.0982</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7449</v>
+        <v>-0.383</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.381</v>
+        <v>0.2848</v>
       </c>
       <c r="V21" t="n">
-        <v>0.315</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0.315</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9528</v>
+        <v>0.7329</v>
       </c>
       <c r="E22" t="n">
-        <v>0.389</v>
+        <v>0.09520000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5638</v>
+        <v>0.6377</v>
       </c>
       <c r="G22" t="n">
         <v>-0.434</v>
@@ -2170,13 +2170,13 @@
         <v>0.3706</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3862</v>
+        <v>0.1663</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3246</v>
+        <v>0.0308</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0617</v>
+        <v>0.1355</v>
       </c>
       <c r="V22" t="n">
         <v>0.63</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.6762</v>
+        <v>-0.5686</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2495</v>
+        <v>-0.0443</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.9257</v>
+        <v>-0.5243</v>
       </c>
       <c r="G25" t="n">
         <v>1.0508</v>
@@ -2404,13 +2404,13 @@
         <v>1.297</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.2447</v>
+        <v>-0.1371</v>
       </c>
       <c r="T25" t="n">
-        <v>0.1057</v>
+        <v>-0.1881</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.3504</v>
+        <v>0.051</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-1.6744</v>
+        <v>-1.7483</v>
       </c>
       <c r="E26" t="n">
         <v>-0.7558</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.9187</v>
+        <v>-0.9925</v>
       </c>
       <c r="G26" t="n">
         <v>-0.7323</v>
@@ -2482,13 +2482,13 @@
         <v>0.1853</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.201</v>
+        <v>-0.2748</v>
       </c>
       <c r="T26" t="n">
         <v>-0.1641</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.0368</v>
+        <v>-0.1107</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>28.7062</v>
+        <v>30.6648</v>
       </c>
       <c r="E27" t="n">
-        <v>16.264</v>
+        <v>16.2639</v>
       </c>
       <c r="F27" t="n">
-        <v>12.4423</v>
+        <v>14.401</v>
       </c>
       <c r="G27" t="n">
         <v>26.6571</v>
@@ -2560,13 +2560,13 @@
         <v>14.823</v>
       </c>
       <c r="S27" t="n">
-        <v>2.3129</v>
+        <v>4.271599999999999</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.5221000000000002</v>
+        <v>-0.5221999999999999</v>
       </c>
       <c r="U27" t="n">
-        <v>2.8351</v>
+        <v>4.793600000000001</v>
       </c>
       <c r="V27" t="n">
         <v>2.5155</v>
@@ -2575,7 +2575,7 @@
         <v>2.8294</v>
       </c>
       <c r="X27" t="n">
-        <v>-0.3138999999999998</v>
+        <v>-0.3139</v>
       </c>
     </row>
   </sheetData>
